--- a/healthcare_assessment_forms/002_hernia_and_varicose_vein_assessment--healthcare_assessment_forms.xlsx
+++ b/healthcare_assessment_forms/002_hernia_and_varicose_vein_assessment--healthcare_assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -803,8 +803,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -832,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'pain',_'value':_'pain'}</t>
+          <t>pain</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Pain', 'value': 'Pain'}</t>
+          <t>Pain</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'fatigue',_'value':_'fatigue'}</t>
+          <t>fatigue</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Fatigue', 'value': 'Fatigue'}</t>
+          <t>Fatigue</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'redness',_'value':_'redness'}</t>
+          <t>redness</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Redness', 'value': 'Redness'}</t>
+          <t>Redness</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'left',_'value':_'left'}</t>
+          <t>left</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Left', 'value': 'left'}</t>
+          <t>Left</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'right',_'value':_'right'}</t>
+          <t>right</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Right', 'value': 'right'}</t>
+          <t>Right</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'both',_'value':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Both', 'value': 'both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'medication',_'value':_'medication'}</t>
+          <t>medication</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Medication', 'value': 'Medication'}</t>
+          <t>Medication</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'surgery',_'value':_'surgery'}</t>
+          <t>surgery</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Surgery', 'value': 'Surgery'}</t>
+          <t>Surgery</t>
         </is>
       </c>
     </row>
@@ -968,12 +968,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
